--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45726</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45345</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46013</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45173</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44764</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45274</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46029</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>46182</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>46085</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45749</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44972</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>45422</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>44969</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44501</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44470</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44706</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44880</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44588</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44849</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>44496</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>44517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>44614</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44727</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44659</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44824</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44496</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44498</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44706</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44725</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44459</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44692</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44616</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44882</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>44792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44797</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44462</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44706</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44530</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44515</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44706</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44658</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44789</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44859</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45400</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45400</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45359</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45751</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>44579</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44902</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45334</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45609</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45411</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45594</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44726</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44981</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45432</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45610</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45361</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45021</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45363</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45544</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45544</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45736</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45354</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45266</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>45737</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45420</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>44895</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44517</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44898</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45688</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45111</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45569</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45610</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45645</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45111</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45559</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44832</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45726</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45726</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44588</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>45000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45274</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45376</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45322</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45726</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44658</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45530</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45411</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45034</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45730</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45191</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45191</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45194</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45194</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45167</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45559</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45238</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45615</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>44486</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45734</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45747</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45698</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45113</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45747</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45735</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45884</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44613</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45211</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45797</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45390</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45099</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45054</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45180</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45790</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45354</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45867</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45407</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45300</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45160</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45160</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45370</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45547</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45547</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44930</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45855</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45884</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45678</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45898</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45898</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45898</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45751</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45630</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45789</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45904</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45020</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45609</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45911</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45911</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45250</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45911</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45911</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45609</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45791</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45747</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45091</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44937</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45918</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45918</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45636</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45485</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45489</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45021</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>45561</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45376</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45831</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>46142</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>44942</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>46142</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46142</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44494</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44970</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45645</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45644</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>46146</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45572</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44617</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44837</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44616</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>44859</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44614</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44797</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>46149</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>46149</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44970</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45751</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45763</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>46149</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44897</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>46150</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45952</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45953</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>44806</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>45002</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45959</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45250</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45964</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45964</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>44564</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44860</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45968</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45432</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45979</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45533</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45988</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45980</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45386</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44981</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45738</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45982</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44964</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45114</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45902</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>46163</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44895</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>44603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45993</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45160</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46163</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45952</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46001</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46001</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46001</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46002</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>46002</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45751</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45069</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45236</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45236</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>46002</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>46006</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45560</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>46006</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45194</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45371</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45149</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46008</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>46009</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45364</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45000</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45628</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45709</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45693</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45701</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46169</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45742</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45585</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45526</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44830</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>44806</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45555</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>46035</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>46174</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45485</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45485</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45785</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46034</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45000</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>46175</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45062</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44463</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>44872</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45737</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45834</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45362</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45358</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46175</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45120</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45726</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46175</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45091</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45588</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46056</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45411</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45726</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45763</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45166</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45565</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45357</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46064</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45191</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45267</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>46072</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46066</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>46076</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>46066</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>46066</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>46183</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>46079</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44698</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46078</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>44987</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45181</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>46085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46085</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>46085</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46085</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46090</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45474</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45538</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>46092</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45420</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46094</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45588</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46196</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45243</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46106</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46106</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>46106</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45099</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45082</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45043</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>46199</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>46199</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45518</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46111</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>46199</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45069</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45069</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>46120</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45544</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45316</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>46199</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>44837</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45098</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45180</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44615</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45775</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45972</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>44964</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45167</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45621</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45029</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>44811</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46206</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>45370</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45372</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>46251</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>46205</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>45453</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45224</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46209</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45245</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45223</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45056</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44958</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>45485</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>46209</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45572</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44953</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45391</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>46254</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>46254</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>45474</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>45433</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45726</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>46259</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45176</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45609</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>44987</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45720</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44855</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44964</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>44964</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45544</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45516</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45082</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45491</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44950</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46260</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45400</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46259</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44849</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>44785</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>46267</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45736</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46267</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46267</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>46267</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45734</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>46269</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45705</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45342</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>46273</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45523</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>46253</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>46274</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>46274</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>46253</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>46274</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>46274</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46274</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46231</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45784</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46279</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45086</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45120</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45784</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45629</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46279</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45384</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45572</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45531</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45791</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45266</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45791</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45559</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>46092</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>45182</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45211</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>46282</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45810</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45810</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45814</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45726</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45820</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45824</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45824</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>45825</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45726</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45737</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45726</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45737</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>45736</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>45827</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45726</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45832</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45832</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>45834</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45840</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45785</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45854</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45615</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45867</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45160</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45868</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45803</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45615</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45877</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45734</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>44711</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44658</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44474</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44559</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45422</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44658</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45422</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44658</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>44630</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45422</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>44974</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>44711</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44782</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44967</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44967</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>45002</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>45369</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>45008</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44706</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>44712</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>44993</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45422</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45015</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44711</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>44559</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>44980</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44990</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44658</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45427</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>44997</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45422</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>44559</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45387</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>44967</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45081</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>44957</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45422</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>44711</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45008</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>44974</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>44671</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44481</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45789</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45786</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45786</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45786</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45627</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45687</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45826</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45853</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45888</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45891</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45693</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45483</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>46081</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>46081</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>46083</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>46083</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>46100</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46099</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46099</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>46119</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>46206</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46273</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45726</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45345</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46013</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45173</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>46029</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45804</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46085</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>45733</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>46006</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45749</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46274</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44764</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44706</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45422</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44969</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>44501</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>44470</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>44706</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44687</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44880</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44588</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>44849</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>44530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>44727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44659</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>44498</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44706</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44692</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>44491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>44882</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>44488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44797</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>44706</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44530</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44872</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44645</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44614</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44813</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44859</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44988</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45411</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45763</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>45734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44837</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44849</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45386</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45069</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45420</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45267</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44517</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45693</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>45709</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45113</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45211</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45182</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45485</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45099</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46034</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45485</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45485</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45180</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45615</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45785</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45888</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>46035</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45734</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44895</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>44872</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45474</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45043</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45898</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45898</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>44915</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45898</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45358</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45357</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45354</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46056</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44964</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45518</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45918</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45516</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>46064</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45544</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45544</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45544</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45120</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>46072</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45432</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45364</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>46066</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>46066</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44950</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44942</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>46066</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46076</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45194</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45194</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>46078</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>46079</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45688</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>46085</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>46085</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45810</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>46085</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>46090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45547</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45547</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46092</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45938</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45021</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45938</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>46094</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45453</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45810</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>44987</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44754</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45737</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45559</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45952</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>46106</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>46106</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45953</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>46106</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45953</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45953</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45959</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46120</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45098</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45964</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45964</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45629</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44981</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45609</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45594</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>45968</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>44897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45814</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45056</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44494</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45166</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44970</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45980</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>44974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45979</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45982</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45565</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45630</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45000</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45993</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45645</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45149</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45736</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45952</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45884</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45995</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44785</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45735</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44615</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44970</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45726</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45120</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45747</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46001</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46002</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>46002</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>46001</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>46002</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45972</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46001</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44804</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>46006</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46006</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44832</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45791</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45867</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45855</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45820</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>46008</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44895</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45742</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45224</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>46009</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45775</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45176</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45615</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45701</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45747</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45824</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45824</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45790</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45678</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45789</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45236</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45236</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45730</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45831</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45825</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45698</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>46142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>46142</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45737</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45736</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45726</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45726</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45737</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44915</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45726</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45526</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45827</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45736</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45737</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>46142</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45243</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44930</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45091</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>46150</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46149</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>46149</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45832</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45832</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>46149</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45400</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45400</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45400</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45738</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45751</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45376</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45491</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45223</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45555</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45840</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45000</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45034</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45902</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45566</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>46164</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44958</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44958</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>46163</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45846</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>44486</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>46168</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45854</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45615</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>46169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>46169</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45371</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45322</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45834</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44806</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45785</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45530</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45062</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44517</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45002</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>44964</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>46175</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>46175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>46175</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45111</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>46174</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45275</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45020</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46174</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45160</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45538</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45868</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45867</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45615</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44579</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45167</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>46183</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45803</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45370</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45585</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45588</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45191</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45191</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45751</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45560</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45334</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45021</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>44806</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45509</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45877</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>46196</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45160</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45160</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45420</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46199</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45181</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>46199</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46199</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46199</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45734</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45610</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44603</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44613</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46205</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45884</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45726</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45726</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46251</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45167</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46206</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45091</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>46209</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45636</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46206</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45609</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45211</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>46209</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45751</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45362</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45407</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45191</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>46254</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45376</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46254</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44616</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46259</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45250</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45238</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45400</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45300</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>46259</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45167</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45180</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45245</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44797</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46267</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>44979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>46267</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>46267</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>46267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45361</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46269</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46274</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>46274</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46231</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46274</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>46274</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46253</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46274</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45082</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>44964</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45763</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46273</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>46253</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46279</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46279</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>44698</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45359</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45610</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46282</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45561</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46092</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>46286</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45391</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45559</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44953</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45432</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44859</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45069</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45069</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>44588</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>44658</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44749</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46289</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44564</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45363</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44726</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45316</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45274</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45111</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44964</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45726</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45747</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45099</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44981</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45370</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45533</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45485</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>44860</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45082</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>44953</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>44937</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45569</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45628</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45621</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>45211</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>45644</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45751</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45354</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45737</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45411</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>44903</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45720</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>44902</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>45726</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45726</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45645</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45572</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45474</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45372</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>44981</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45544</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44898</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45713</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45609</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45433</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44617</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45726</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44574</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45000</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45609</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>44837</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45194</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45705</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45784</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45342</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45523</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45120</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45784</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45629</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45086</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45384</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45572</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45266</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45531</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45791</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45791</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>45559</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44711</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44658</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>44559</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>44658</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>44658</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>44630</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44711</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>44706</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>44712</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44711</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44559</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>44658</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44559</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44711</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>44671</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44474</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45422</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45422</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45422</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>44974</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>44782</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>44967</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44967</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45002</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>45369</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45008</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44993</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>45422</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45015</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45422</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>44980</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>44990</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45427</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>44997</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45422</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45387</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>44967</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45081</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>44957</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45422</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45008</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>44974</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44481</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45786</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45786</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45789</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45786</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45826</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45627</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45687</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45853</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45888</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45891</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>45693</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>45483</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>46081</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46081</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46083</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>46083</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46099</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46099</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>46100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46119</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>46206</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>46273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>46289</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>46289</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45726</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45345</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46013</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45173</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>46029</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45804</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46085</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>45733</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>46006</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45749</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46274</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44764</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44706</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45422</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44969</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>44501</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>44470</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>44706</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44687</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44880</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44588</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>44849</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>44530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>44727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44659</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>44498</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44706</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44692</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>44491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>44882</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>44488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44797</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>44706</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44530</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44872</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44645</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44614</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44813</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44859</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44988</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45411</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45763</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>45734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44837</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44849</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45386</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45069</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45420</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45267</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44517</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45693</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>45709</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45113</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45211</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45182</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45485</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45099</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46034</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45485</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45485</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45180</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45615</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45785</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45888</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>46035</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45734</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44895</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>44872</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45474</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45043</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45898</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45898</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>44915</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45898</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45358</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45357</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45354</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46056</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44964</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45518</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45918</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45516</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>46064</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45544</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45544</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45544</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45120</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>46072</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45432</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45364</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>46066</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>46066</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44950</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44942</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>46066</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46076</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45194</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45194</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>46078</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>46079</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45688</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>46085</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>46085</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45810</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>46085</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>46090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45547</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45547</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46092</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45938</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45021</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45938</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>46094</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45453</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45810</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>44987</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44754</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45737</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45559</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45952</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>46106</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>46106</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45953</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>46106</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45953</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45953</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45959</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46120</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45098</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45964</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45964</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45629</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44981</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45609</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45594</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>45968</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>44897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45814</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45056</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44494</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45166</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44970</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45980</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>44974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45979</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45982</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45565</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45630</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45000</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45993</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45645</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45149</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45736</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45952</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45884</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45995</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44785</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45735</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44615</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44970</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45726</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45120</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45747</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46001</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46002</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>46002</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>46001</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>46002</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45972</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46001</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44804</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>46006</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46006</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44832</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45791</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45867</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45855</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45820</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>46008</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44895</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45742</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45224</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>46009</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45775</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45176</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45615</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45701</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45747</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45824</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45824</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45790</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45678</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45789</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45236</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45236</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45730</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45831</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45825</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45698</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>46142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>46142</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45737</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45736</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45726</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45726</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45737</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44915</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45726</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45526</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45827</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45736</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45737</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>46142</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45243</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44930</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45091</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>46150</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46149</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>46149</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45832</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45832</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>46149</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45400</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45400</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45400</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45738</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45751</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45376</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45491</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45223</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45555</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45840</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45000</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45034</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45902</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45566</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>46164</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44958</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44958</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>46163</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45846</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>44486</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>46168</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45854</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45615</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>46169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>46169</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45371</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45322</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45834</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44806</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45785</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45530</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45062</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44517</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45002</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>44964</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>46175</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>46175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>46175</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45111</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>46174</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45275</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45020</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46174</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45160</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45538</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45868</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45867</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45615</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44579</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45167</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>46183</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45803</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45370</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45585</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45588</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45191</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45191</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45751</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45560</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45334</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45021</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>44806</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45509</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45877</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>46196</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45160</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45160</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45420</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46199</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45181</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>46199</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46199</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46199</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45734</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45610</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44603</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44613</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46205</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45884</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45726</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45726</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46251</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45167</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46206</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45091</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>46209</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45636</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46206</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45609</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45211</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>46209</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45751</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45362</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45407</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45191</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>46254</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45376</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46254</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44616</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46259</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45250</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45238</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45400</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45300</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>46259</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45167</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45180</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45245</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44797</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46267</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>44979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>46267</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>46267</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>46267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45361</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46269</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46274</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>46274</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46231</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46274</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>46274</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46253</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46274</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45082</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>44964</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45763</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46273</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>46253</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46279</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46279</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>44698</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45359</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45610</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46282</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45561</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46092</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>46286</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45391</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45559</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44953</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45432</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44859</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45069</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45069</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>44588</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>44658</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44749</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46289</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44564</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45363</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44726</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45316</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45274</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45111</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44964</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45726</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45747</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45099</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44981</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45370</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45533</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45485</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>44860</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45082</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>44953</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>44937</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45569</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45628</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45621</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>45211</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>45644</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45751</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45354</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45737</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45411</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>44903</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45720</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>44902</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>45726</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45726</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45645</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45572</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45474</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45372</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>44981</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45544</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44898</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45713</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45609</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45433</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44617</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45726</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44574</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45000</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45609</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>44837</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45194</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45705</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45784</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45342</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45523</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45120</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45784</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45629</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45086</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45384</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45572</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45266</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45531</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45791</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45791</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>45559</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44711</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44658</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>44559</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>44658</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>44658</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>44630</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44711</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>44706</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>44712</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44711</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44559</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>44658</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44559</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44711</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>44671</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44474</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45422</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45422</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45422</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>44974</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>44782</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>44967</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44967</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45002</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>45369</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45008</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44993</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>45422</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45015</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45422</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>44980</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>44990</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45427</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>44997</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45422</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45387</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>44967</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45081</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>44957</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45422</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45008</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>44974</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44481</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45786</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45786</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45789</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45786</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45826</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45627</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45687</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45853</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45888</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45891</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>45693</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>45483</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>46081</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46081</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46083</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>46083</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46099</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46099</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>46100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46119</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>46206</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>46273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>46289</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>46289</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45831</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>46296</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>45804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45733</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>46288</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44475</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44882</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44488</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44792</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>44797</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44789</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>44530</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>44706</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44530</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>44883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>44515</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44706</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44658</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44789</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44859</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45400</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45400</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45751</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45359</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45334</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44902</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>44726</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45609</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44981</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45021</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45432</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45211</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45361</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45544</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45544</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45266</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44901</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45884</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45384</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45572</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45736</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>46006</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45531</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45791</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>46006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45615</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45785</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45509</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45354</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>46008</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46009</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45113</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45737</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45420</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45693</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45266</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45701</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45791</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45888</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45559</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44937</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>46035</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45898</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44981</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44517</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45904</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44898</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45911</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45911</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45911</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45911</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45211</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45569</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45358</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45911</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45688</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44988</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45918</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45918</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45629</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46056</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45610</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45181</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45645</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45111</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46064</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45559</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45251</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45726</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45938</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44832</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44588</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45099</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45938</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45274</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>46072</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45210</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45376</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46066</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45726</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44517</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45810</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46066</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>44658</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>44754</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>46066</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45275</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45322</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>46079</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>46078</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45048</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45953</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45953</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46085</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>46085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>46085</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>46090</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45411</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45959</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>46092</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46094</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>45730</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45964</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>45167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45814</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45191</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45191</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45968</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45167</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45194</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45194</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46106</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45726</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>46106</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45979</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45980</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45982</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45820</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>46111</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45238</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45559</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45824</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45824</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>46120</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45825</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45726</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45737</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45726</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44486</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45993</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45995</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45952</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45737</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>45737</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45736</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45120</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45827</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45726</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45211</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45832</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45390</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45354</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45832</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45713</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45407</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45834</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45834</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>44615</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45300</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45775</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45160</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45160</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45370</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45547</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45547</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44930</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45840</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>45751</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45107</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45630</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45785</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45846</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45698</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45020</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45747</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45609</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45250</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45735</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45609</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45884</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45797</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>44979</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45747</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45854</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45790</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44974</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45615</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44937</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45867</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45636</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45485</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45489</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45021</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45561</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45376</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45789</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44942</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44494</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44970</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45615</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45645</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45644</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45572</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45867</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45160</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44617</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45566</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44837</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44915</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44616</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45791</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44859</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44614</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45868</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44797</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44970</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45751</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44897</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>46142</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46142</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45803</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46146</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>46149</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46149</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>44806</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>46149</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>46150</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45002</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45250</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>44564</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45988</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45738</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44860</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45902</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45432</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46163</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>46163</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>46164</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45533</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45877</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45386</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44981</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>46168</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46169</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>46174</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>46174</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45785</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45734</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>46175</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45834</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>46174</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>44964</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>46175</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>46175</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45114</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>46175</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45734</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44613</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45054</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45180</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44895</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44603</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45160</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46183</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45751</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45069</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45236</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45236</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45560</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45194</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45371</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45364</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46196</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45000</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45628</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45742</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46199</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45585</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46199</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45526</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44804</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>44830</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>44806</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45555</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46206</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45485</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45485</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>46206</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46205</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45000</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46209</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44872</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45737</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>44915</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45362</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45120</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45726</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>45091</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45588</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46260</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45411</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45726</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45763</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>46259</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>46267</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45166</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45565</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45357</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45191</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>46267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45267</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46269</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45160</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>46273</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>44698</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45069</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>46274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>46274</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44987</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45181</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>46274</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>46274</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>46274</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>46231</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46279</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46279</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45474</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45538</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45420</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>46282</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45588</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45243</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45099</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45082</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45043</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>46092</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>46286</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>46286</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45518</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45069</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45069</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>46289</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45544</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46293</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45316</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44837</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45098</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45180</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46294</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>46286</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46294</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44574</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44964</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45167</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45621</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45029</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44981</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46251</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>46253</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44811</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45370</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46254</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45372</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>46253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46254</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46297</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>46288</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45453</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45224</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45245</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45223</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45056</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44958</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45485</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45572</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>44953</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45391</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45474</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45433</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45176</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45609</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44987</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>45720</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>44855</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>44964</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>44964</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45544</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45516</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45082</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45491</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>44950</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45400</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44849</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44785</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45736</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>45211</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45734</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45705</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45342</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45523</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45784</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45086</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45120</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45784</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45629</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44711</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44658</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44474</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45422</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45422</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>44658</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44630</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44974</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44711</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44782</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44967</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44967</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45002</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45369</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45008</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>44706</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44712</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44993</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45422</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45015</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>44711</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44559</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45422</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44980</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44990</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44658</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45427</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44997</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45422</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44559</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>45387</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>44967</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45081</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44957</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45422</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44711</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45008</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>44974</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44671</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>44481</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45789</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45786</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45786</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45627</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45826</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45853</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45888</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45891</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45693</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45483</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46081</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46100</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46099</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46289</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45831</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>46296</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>45804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45733</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>46288</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44475</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44882</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44488</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44792</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>44797</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44789</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>44530</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>44706</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44530</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>44883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>44515</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44706</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44658</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44789</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44859</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45400</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45400</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45751</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45359</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45334</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44902</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>44726</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45609</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44981</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45021</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45432</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45211</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45361</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45544</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45544</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45266</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44901</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45884</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45384</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45572</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45736</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>46006</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45531</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45791</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>46006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45615</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45785</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45509</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45354</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>46008</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46009</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45113</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45737</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45420</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45693</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45266</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45701</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45791</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45888</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45559</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44937</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>46035</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45898</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44981</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44517</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45904</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44898</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45911</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45911</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45911</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45911</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45211</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45569</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45358</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45911</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45688</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44988</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45918</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45918</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45629</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46056</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45610</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45181</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45645</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45111</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46064</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45559</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45251</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45726</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45938</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44832</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44588</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45099</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45938</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45274</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>46072</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45210</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45376</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46066</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45726</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44517</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45810</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46066</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>44658</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>44754</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>46066</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45275</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45322</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>46079</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>46078</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45048</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45953</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45953</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46085</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>46085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>46085</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>46090</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45411</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45959</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>46092</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46094</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>45730</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45964</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>45167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45814</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45191</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45191</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45968</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45167</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45194</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45194</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46106</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45726</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>46106</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45979</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45980</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45982</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45820</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>46111</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45238</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45559</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45824</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45824</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>46120</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45825</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45726</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45737</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45726</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44486</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45993</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45995</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45952</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45737</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>45737</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45736</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45120</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45827</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45726</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45211</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45832</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45390</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45354</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45832</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45713</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45407</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45834</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45834</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>44615</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45300</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45775</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45160</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45160</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45370</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45547</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45547</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44930</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45840</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>45751</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45107</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45630</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45785</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45846</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45698</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45020</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45747</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45609</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45250</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45735</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45609</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45884</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45797</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>44979</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45747</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45854</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45790</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44974</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45615</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44937</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45867</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45636</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45485</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45489</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45021</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45561</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45376</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45789</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44942</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44494</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44970</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45615</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45645</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45644</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45572</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45867</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45160</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44617</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45566</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44837</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44915</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44616</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45791</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44859</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44614</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45868</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44797</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44970</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45751</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44897</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>46142</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46142</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45803</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46146</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>46149</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46149</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>44806</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>46149</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>46150</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45002</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45250</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>44564</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45988</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45738</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44860</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45902</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45432</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46163</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>46163</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>46164</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45533</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45877</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45386</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44981</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>46168</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46169</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>46174</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>46174</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45785</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45734</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>46175</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45834</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>46174</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>44964</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>46175</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>46175</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45114</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>46175</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45734</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44613</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45054</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45180</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44895</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44603</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45160</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46183</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45751</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45069</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45236</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45236</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45560</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45194</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45371</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45364</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46196</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45000</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45628</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45742</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46199</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45585</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46199</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45526</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44804</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>44830</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>44806</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45555</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46206</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45485</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45485</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>46206</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46205</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45000</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46209</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44872</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45737</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>44915</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45362</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45120</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45726</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>45091</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45588</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46260</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45411</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45726</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45763</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>46259</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>46267</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45166</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45565</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45357</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45191</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>46267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45267</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46269</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45160</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>46273</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>44698</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45069</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>46274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>46274</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44987</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45181</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>46274</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>46274</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>46274</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>46231</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46279</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46279</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45474</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45538</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45420</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>46282</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45588</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45243</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45099</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45082</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45043</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>46092</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>46286</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>46286</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45518</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45069</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45069</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>46289</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45544</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46293</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45316</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44837</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45098</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45180</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46294</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>46286</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46294</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44574</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44964</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45167</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45621</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45029</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44981</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46251</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>46253</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44811</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45370</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46254</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45372</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>46253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46254</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46297</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>46288</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45453</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45224</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45245</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45223</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45056</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44958</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45485</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45572</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>44953</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45391</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45474</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45433</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45176</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45609</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44987</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>45720</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>44855</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>44964</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>44964</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45544</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45516</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45082</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45491</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>44950</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45400</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44849</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44785</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45736</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>45211</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45734</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45705</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45342</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45523</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45784</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45086</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45120</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45784</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45629</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44711</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44658</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44474</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45422</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45422</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>44658</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44630</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44974</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44711</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44782</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44967</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44967</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45002</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45369</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45008</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>44706</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44712</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44993</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45422</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45015</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>44711</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44559</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45422</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44980</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44990</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44658</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45427</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44997</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45422</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44559</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>45387</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>44967</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45081</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44957</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45422</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44711</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45008</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>44974</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44671</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>44481</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45789</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45786</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45786</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45627</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45826</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45853</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45888</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45891</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45693</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45483</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46081</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46100</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46099</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46289</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45831</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>46296</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>45749</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45804</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>46006</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44764</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46203</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46288</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44789</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44792</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44797</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44530</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44789</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44616</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44692</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44515</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44883</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44882</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44515</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44488</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44524</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44638</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44658</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44517</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45091</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45160</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45411</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44859</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45485</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44860</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45763</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45400</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45400</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45400</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45082</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44837</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44849</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45751</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45376</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45569</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45223</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44811</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45628</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45621</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45555</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45211</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45644</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45354</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45386</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45737</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45411</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45250</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45411</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45420</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45566</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>44830</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>44903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>44902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45267</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44486</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44613</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44517</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45726</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45726</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45572</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45884</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45474</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45372</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44981</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45544</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45713</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45113</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45609</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45433</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44901</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45054</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45210</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45371</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45322</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45180</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45726</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44806</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45615</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44517</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45734</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45114</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44574</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45111</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45485</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45275</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45000</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45609</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44837</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45898</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45898</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45538</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45485</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45485</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44895</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44872</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45474</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45904</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45194</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45544</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45043</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44579</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45705</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45107</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45911</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45911</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45911</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45911</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45911</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44987</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45342</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45523</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44614</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45357</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45120</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45354</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45918</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>45629</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45518</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45918</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45086</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45585</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45588</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45191</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45191</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45516</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45384</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45544</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45544</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45544</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45572</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45120</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>45751</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45560</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45334</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>45021</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>44806</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45531</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>45509</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45432</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45364</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45791</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>44950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44942</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45559</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45194</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45194</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45688</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45160</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45160</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45160</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45420</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45547</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45588</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45610</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44603</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45021</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45390</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45453</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45726</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45167</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45091</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45636</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44754</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45938</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45609</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45938</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45211</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45737</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45559</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45751</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45810</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45362</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45407</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45251</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45814</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45726</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>45820</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45069</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45098</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45824</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45824</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45376</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45629</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44981</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44616</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45825</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45609</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45737</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45736</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45726</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45594</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45726</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45737</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45726</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45737</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>44897</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45832</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45953</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45953</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45832</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45056</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44494</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45250</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45964</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45834</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45834</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45238</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45166</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44970</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45840</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45400</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44974</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45565</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45630</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45785</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45846</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45099</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45300</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45000</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45167</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45180</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45245</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45645</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45149</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45736</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45854</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45615</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44797</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44979</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44785</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>44970</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45120</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45160</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45868</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45867</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44804</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>44832</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45361</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45803</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45742</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45224</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45082</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>45176</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45763</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45979</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45877</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45982</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45678</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45236</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45236</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45734</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45730</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44698</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45359</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45610</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45985</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44937</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44915</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>45181</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46106</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45526</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45572</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45736</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45561</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45243</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45391</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45993</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45559</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>46120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>44953</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45952</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45995</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>46001</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46002</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46002</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>46001</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45432</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44859</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46006</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45069</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45069</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46006</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>46006</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>44588</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>44658</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>44749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46009</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44564</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45363</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45701</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45693</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45709</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45884</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45735</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44726</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44615</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45747</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45316</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45274</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45972</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46034</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45791</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45855</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>46035</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44964</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45726</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45747</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45775</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45615</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45747</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>45790</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45789</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45099</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>44981</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45370</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45533</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45831</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45797</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45266</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45698</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45358</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>46142</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>46142</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>46056</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>46142</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>46146</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>46064</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46150</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>46149</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>46149</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>46149</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>46072</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46066</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46066</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>46066</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46076</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>46078</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46079</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45048</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46085</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46085</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46085</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>46085</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45738</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>46090</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>46092</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45902</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>46164</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>46163</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>46163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>46169</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46169</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45834</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45785</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>46174</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>46175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>46175</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46175</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46174</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>46175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46196</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46199</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46206</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>46209</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>46206</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>46209</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>46259</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>46267</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>46267</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>46267</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46267</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>46269</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>46274</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46274</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>46231</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>46274</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>46274</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>46274</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>46273</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46279</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46279</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46282</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46286</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46293</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>46294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>46294</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>46253</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46253</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46251</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46254</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46254</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46183</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46297</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>46092</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>46199</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46301</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46301</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>46259</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>46260</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46304</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>46304</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44711</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44658</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44658</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44630</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>44711</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44706</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>44712</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44711</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44559</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44658</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44559</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44711</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44671</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45422</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45422</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44974</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44782</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>44967</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44967</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45002</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45369</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45008</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44993</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45422</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45015</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45422</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44980</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44990</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45427</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44997</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45422</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>45387</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44967</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45081</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44957</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45422</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45008</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44974</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>44481</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45786</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45789</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45786</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45826</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45627</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45687</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45853</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45888</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45891</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45693</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45483</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46081</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46100</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46289</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45831</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>46296</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>45749</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45804</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>46006</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44764</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46203</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46288</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44789</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44792</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44797</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44530</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44789</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44616</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44692</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44515</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44883</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44882</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44515</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44488</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44524</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44638</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44658</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44517</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45091</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45160</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45411</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44859</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45485</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44860</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45763</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45400</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45400</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45400</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45082</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44837</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44849</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45751</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45376</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45569</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45223</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44811</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45628</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45621</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45555</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45211</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45644</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45354</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45386</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45737</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45411</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45250</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45411</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45420</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45566</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>44830</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>44903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>44902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45267</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44486</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44613</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44517</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45726</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45726</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45572</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45884</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45474</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45372</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44981</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45544</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45713</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45113</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45609</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45433</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44901</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45054</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45210</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45371</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45322</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45180</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45726</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44806</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45615</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44517</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45734</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45114</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44574</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45111</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45485</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45275</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45000</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45609</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44837</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45898</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45898</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45538</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45485</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45485</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44895</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44872</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45474</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45904</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45194</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45544</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45043</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44579</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45705</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45107</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45911</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45911</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45911</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45911</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45911</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44987</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45342</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45523</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44614</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45357</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45120</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45354</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45918</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>45629</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45518</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45918</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45086</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45585</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45588</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45191</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45191</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45516</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45384</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45544</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45544</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45544</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45572</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45120</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>45751</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45560</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45334</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>45021</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>44806</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45531</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>45509</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45432</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45364</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45791</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>44950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44942</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45559</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45194</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45194</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45688</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45160</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45160</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45160</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45420</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45547</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45588</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45610</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44603</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45021</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45390</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45453</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45726</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45167</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45091</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45636</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44754</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45938</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45609</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45938</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45211</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45737</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45559</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45751</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45810</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45362</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45407</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45251</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45814</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45726</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>45820</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45069</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45098</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45824</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45824</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45376</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45629</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44981</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44616</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45825</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45609</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45737</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45736</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45726</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45594</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45726</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45737</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45726</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45737</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>44897</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45832</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45953</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45953</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45832</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45056</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44494</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45250</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45964</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45834</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45834</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45238</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45166</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44970</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45840</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45400</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44974</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45565</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45630</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45785</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45846</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45099</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45300</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45000</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45167</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45180</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45245</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45645</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45149</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45736</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45854</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45615</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44797</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44979</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44785</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>44970</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45120</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45160</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45868</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45867</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44804</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>44832</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45361</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45803</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45742</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45224</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45082</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>45176</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45763</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45979</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45877</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45982</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45678</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45236</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45236</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45734</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45730</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44698</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45359</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45610</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45985</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44937</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44915</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>45181</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46106</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45526</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45572</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45736</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45561</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45243</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45391</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45993</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45559</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>46120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>44953</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45952</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45995</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>46001</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46002</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46002</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>46001</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45432</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44859</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46006</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45069</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45069</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46006</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>46006</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>44588</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>44658</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>44749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46009</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44564</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45363</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45701</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45693</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45709</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45884</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45735</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44726</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44615</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45747</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45316</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45274</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45972</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46034</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45791</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45855</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>46035</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44964</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45726</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45747</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45775</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45615</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45747</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>45790</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45789</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45099</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>44981</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45370</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45533</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45831</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45797</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45266</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45698</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45358</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>46142</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>46142</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>46056</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>46142</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>46146</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>46064</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46150</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>46149</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>46149</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>46149</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>46072</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46066</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46066</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>46066</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46076</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>46078</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46079</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45048</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46085</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46085</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46085</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>46085</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45738</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>46090</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>46092</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45902</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>46164</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>46163</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>46163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>46169</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46169</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45834</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45785</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>46174</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>46175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>46175</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46175</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46174</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>46175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46196</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46199</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46206</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>46209</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>46206</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>46209</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>46259</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>46267</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>46267</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>46267</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46267</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>46269</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>46274</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46274</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>46231</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>46274</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>46274</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>46274</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>46273</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46279</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46279</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46282</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46286</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46293</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>46294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>46294</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>46253</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46253</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46251</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46254</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46254</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46183</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46297</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>46092</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>46199</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46301</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46301</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>46259</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>46260</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46304</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>46304</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44711</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44658</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44658</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44630</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>44711</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44706</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>44712</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44711</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44559</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44658</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44559</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44711</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44671</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45422</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45422</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44974</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44782</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>44967</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44967</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45002</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45369</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45008</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44993</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45422</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45015</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45422</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44980</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44990</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45427</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44997</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45422</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>45387</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44967</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45081</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44957</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45422</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45008</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44974</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>44481</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45786</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45789</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45786</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45826</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45627</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45687</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45853</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45888</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45891</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45693</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45483</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46081</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46100</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46289</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45726</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>46296</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46006</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>46203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>46274</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45749</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45733</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44659</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44824</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44496</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44692</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44610</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44616</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44882</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>44488</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44524</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44797</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44706</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44530</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44883</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>44645</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44638</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44658</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44517</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44859</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45400</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45400</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45359</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45751</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44579</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45411</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45334</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45594</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45609</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44981</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45432</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45211</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45361</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45363</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45544</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45736</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45354</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45737</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45420</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44981</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44517</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44898</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45688</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45111</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45569</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45530</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45629</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45610</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45645</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45111</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45251</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45726</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45726</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45559</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44832</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44588</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45000</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45275</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45376</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45726</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44658</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44754</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45322</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45730</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45191</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45191</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45194</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45194</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45615</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45238</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45747</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45559</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45698</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45734</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45747</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45735</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45884</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45797</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45113</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44613</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44486</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45099</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45054</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45180</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45867</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45888</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45120</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45211</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45855</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44901</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45789</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45615</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45354</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45713</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45898</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45791</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45407</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45904</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>45160</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45160</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45831</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45911</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45911</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45911</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45370</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>46142</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>46142</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46142</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45547</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45547</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44930</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45911</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45678</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>46146</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45751</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45630</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45918</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45609</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45250</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45609</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46149</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>46149</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44979</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45747</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46149</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45091</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46150</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44937</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45636</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45489</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45021</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45938</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45376</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44953</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44942</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>44494</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44970</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45952</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45572</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45988</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44617</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45953</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45566</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44837</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>45738</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>44915</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44616</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44859</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44614</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45959</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44797</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45964</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45964</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>44970</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45751</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45763</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44897</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45968</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>46163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>46163</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44806</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45979</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>46164</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45980</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45002</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45982</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45250</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45985</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44564</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44860</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45993</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45432</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>46169</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46168</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45952</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45533</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46169</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46001</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45386</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44981</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46002</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>46002</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>46174</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>46174</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>46006</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45785</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>46006</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46008</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>46009</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>46175</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44964</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45114</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45709</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45693</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45701</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44895</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44603</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>46175</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>46035</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>46175</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>46034</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45751</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45069</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45236</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45236</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45358</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45560</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>45194</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45371</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45149</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>46056</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45364</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45000</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45742</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45585</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45526</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>46072</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>46076</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44804</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44830</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46066</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46066</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>44806</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45555</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44749</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46079</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45485</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45485</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46078</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45048</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46085</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46085</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46085</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46085</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46090</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45000</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45062</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46092</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44872</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45737</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44915</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45362</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45120</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45726</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45588</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>46106</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46106</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46106</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46196</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>45411</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45726</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>45763</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45166</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45565</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45357</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>46199</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45191</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>46120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46199</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45267</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>46199</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45160</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44698</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45069</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>44987</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45181</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44615</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45775</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45972</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46206</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45474</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>46206</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45538</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45420</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>46209</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46209</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45588</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45243</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45099</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45082</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45043</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45518</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45069</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45069</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46273</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45544</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>46274</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>46274</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>46274</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>46274</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>46274</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45316</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>44837</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45098</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>46279</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45180</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>46279</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44574</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44964</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45167</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45621</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45029</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44981</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44811</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45370</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45372</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46282</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45453</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45224</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45245</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45223</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45056</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44958</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>46286</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>46286</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45485</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45572</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44953</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45391</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46289</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45474</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45433</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45726</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45176</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44987</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45720</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44855</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44964</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45544</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45516</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45082</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45491</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44950</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>46294</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>46286</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>46294</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45400</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44849</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>46251</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44785</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45736</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>46253</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45211</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46254</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>46253</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46254</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46297</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45734</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>46183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46199</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45705</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46301</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>46301</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45342</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45523</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45784</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45086</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>45120</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45784</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45629</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>46260</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45384</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45572</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46259</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45531</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45791</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45266</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45791</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46306</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45182</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45211</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>46304</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>46304</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>46092</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>46259</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45810</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>46269</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>46267</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45814</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>46267</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45726</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45820</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45824</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45824</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45825</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45726</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45737</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45726</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46267</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45737</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45737</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45736</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45827</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45726</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>45832</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45834</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>45834</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45840</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45785</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45846</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45854</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45615</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45867</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45160</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45868</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45803</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45615</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45877</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45734</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44711</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44658</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44559</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45422</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44658</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45422</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44658</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>44630</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45422</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44974</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44711</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44782</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44967</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44967</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45002</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45369</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45008</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44706</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44712</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>44993</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45422</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45015</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44711</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44559</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45422</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44980</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44990</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>44658</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45427</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44997</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45422</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>44559</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45387</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44967</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45081</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45422</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>44711</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45008</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44974</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>44671</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45789</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45786</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45786</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45627</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45826</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45853</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45888</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45891</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45693</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45483</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46081</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46100</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46099</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46289</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45726</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>46296</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45831</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46006</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>46203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>46274</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45749</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45733</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44659</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44824</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44496</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44692</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44610</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44616</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44882</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>44488</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44524</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44797</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44706</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44530</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44883</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>44645</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44638</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44658</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44517</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44859</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45400</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45400</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45359</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45751</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44579</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45411</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45334</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45594</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45609</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44981</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45432</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45211</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45361</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45363</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45544</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45736</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45354</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45737</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45420</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44981</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44517</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44898</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45688</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45111</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45569</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45530</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45629</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45610</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45645</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45111</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45251</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45726</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45726</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45559</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44832</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44588</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45000</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45275</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45376</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45726</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44658</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44754</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45322</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45730</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45191</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45191</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45194</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45194</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45615</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45238</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45747</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45559</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45698</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45734</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45747</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45735</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45884</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45797</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45113</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44613</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44486</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45099</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45054</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45180</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45867</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45888</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45120</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45211</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45855</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44901</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45789</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45615</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45354</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45713</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45898</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45791</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45407</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45904</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>45160</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45160</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45831</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45911</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45911</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45911</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45370</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>46142</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>46142</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46142</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45547</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45547</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44930</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45911</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45678</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>46146</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45751</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45630</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45918</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45609</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45250</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45609</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46149</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>46149</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44979</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45747</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46149</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45091</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46150</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44937</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45636</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45489</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45021</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45938</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45376</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44953</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44942</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>44494</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44970</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45952</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45572</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45988</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44617</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45953</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45566</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44837</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>45738</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>44915</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44616</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44859</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44614</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45959</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44797</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45964</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45964</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>44970</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45751</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45763</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44897</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45968</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>46163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>46163</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44806</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45979</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>46164</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45980</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45002</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45982</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45250</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45985</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44564</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44860</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45993</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45432</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>46169</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46168</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45952</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45533</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46169</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46001</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45386</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44981</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46002</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>46002</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>46174</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>46174</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>46006</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45785</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>46006</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46008</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>46009</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>46175</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44964</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45114</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45709</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45693</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45701</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44895</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44603</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>46175</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>46035</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>46175</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>46034</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45751</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45069</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45236</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45236</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45358</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45560</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>45194</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45371</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45149</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>46056</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45364</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45000</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45742</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45585</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45526</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>46072</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>46076</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44804</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44830</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46066</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46066</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>44806</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45555</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44749</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46079</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45485</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45485</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46078</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45048</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46085</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46085</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46085</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46085</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46090</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45000</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45062</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46092</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44872</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45737</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44915</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45362</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45120</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45726</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45588</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>46106</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46106</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46106</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46196</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>45411</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45726</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>45763</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45166</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45565</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45357</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>46199</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45191</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>46120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46199</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45267</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>46199</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45160</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44698</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45069</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>44987</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45181</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44615</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45775</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45972</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46206</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45474</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>46206</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45538</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45420</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>46209</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46209</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45588</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45243</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45099</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45082</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45043</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45518</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45069</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45069</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46273</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45544</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>46274</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>46274</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>46274</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>46274</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>46274</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45316</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>44837</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45098</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>46279</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45180</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>46279</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44574</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44964</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45167</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45621</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45029</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44981</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44811</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45370</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45372</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46282</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45453</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45224</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45245</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45223</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45056</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44958</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>46286</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>46286</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45485</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45572</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44953</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45391</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46289</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45474</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45433</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45726</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45176</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44987</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45720</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44855</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44964</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45544</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45516</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45082</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45491</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44950</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>46294</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>46286</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>46294</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45400</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44849</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>46251</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44785</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45736</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>46253</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45211</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46254</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>46253</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46254</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46297</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45734</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>46183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46199</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45705</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46301</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>46301</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45342</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45523</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45784</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45086</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>45120</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45784</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45629</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>46260</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45384</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45572</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46259</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45531</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45791</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45266</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45791</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46306</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45182</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45211</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>46304</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>46304</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>46092</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>46259</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45810</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>46269</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>46267</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45814</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>46267</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45726</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45820</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45824</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45824</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45825</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45726</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45737</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45726</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46267</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45737</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45737</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45736</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45827</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45726</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>45832</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45834</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>45834</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45840</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45785</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45846</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45854</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45615</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45867</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45160</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45868</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45803</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45615</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45877</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45734</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44711</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44658</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44559</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45422</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44658</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45422</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44658</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>44630</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45422</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44974</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44711</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44782</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44967</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44967</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45002</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45369</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45008</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44706</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44712</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>44993</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45422</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45015</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44711</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44559</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45422</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44980</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44990</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>44658</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45427</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44997</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45422</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>44559</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45387</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44967</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45081</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45422</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>44711</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45008</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44974</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>44671</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45789</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45786</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45786</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45627</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45826</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45853</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45888</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45891</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45693</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45483</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46081</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46100</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46099</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46099</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46289</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46296</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45726</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>46006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>46288</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44496</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44498</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44692</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44610</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44616</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44882</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>44792</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44789</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44797</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44796</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44530</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44883</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44515</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44638</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44706</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44658</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45054</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44859</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45180</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45785</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45888</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45884</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44658</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45734</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44988</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45898</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45898</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44564</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45211</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45363</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45904</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45099</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45411</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45911</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45316</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45274</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45911</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>46164</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>46163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45111</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>46163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>46168</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44964</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45726</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>46169</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>46169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45834</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45785</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45763</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45099</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45370</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>46175</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46175</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45266</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45938</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>46174</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>46175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>46174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44837</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44849</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44902</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44855</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45485</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44860</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45386</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45082</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45250</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45411</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45420</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44830</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44953</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45069</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45267</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45952</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45953</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45569</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45621</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45211</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45953</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45644</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45751</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45354</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45737</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45411</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45964</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45720</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45968</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45726</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45726</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45645</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45572</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45474</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44981</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46196</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44898</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45609</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45433</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44617</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46199</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46199</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44517</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45726</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45979</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45982</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>46205</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45114</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>44574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45000</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45609</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45489</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>44837</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>46209</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>46209</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45194</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45952</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45995</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>46001</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46002</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45705</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46002</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>46002</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46006</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45342</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46006</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46006</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46231</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45523</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45120</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45784</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46008</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>46009</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>46279</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45629</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45086</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45701</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45693</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45709</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45384</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45572</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45266</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45531</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45791</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>46282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>46286</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>46286</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45791</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45559</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45211</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45358</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>46289</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45810</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45810</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46293</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45814</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46294</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>46064</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46294</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>46286</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45726</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46072</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45820</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46066</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46066</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45824</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45824</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46066</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45825</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>46078</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>46079</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45737</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45736</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45726</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45726</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45737</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45726</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45827</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45737</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>46251</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45048</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>46085</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46085</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45832</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45832</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>46085</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46085</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45834</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45834</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46090</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46254</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>46092</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45840</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46183</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45485</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46297</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>46094</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>46199</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45785</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45846</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46301</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46301</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45485</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45485</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>46259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45854</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45615</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>46106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>46111</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44981</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44872</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45474</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45160</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45868</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45867</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45615</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>46120</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>46260</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45043</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45803</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46304</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46304</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45877</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>46306</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45734</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>44613</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>46259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44614</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45357</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45354</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>46092</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44964</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45518</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>46267</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>46267</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>46267</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46267</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45884</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45735</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45747</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45516</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>45972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45544</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45120</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45791</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45867</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>46269</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45432</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46253</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46274</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44950</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44942</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45775</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45194</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45747</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45790</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45789</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>46315</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45688</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45831</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>46315</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45797</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>46273</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45698</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>46253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>46274</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>46142</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46142</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45547</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45547</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45588</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46274</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46142</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45021</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46274</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46146</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45390</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46274</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45453</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46150</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>44987</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46149</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46149</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44754</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>46149</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>45737</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45559</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45251</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45988</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45738</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45069</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45098</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45629</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>44981</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45609</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45594</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44897</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45056</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44494</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45166</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>44970</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45565</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45630</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45000</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45645</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45149</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45736</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>44970</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>45120</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44804</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>44832</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44895</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45742</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45224</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45176</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45678</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45236</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45236</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45730</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>44937</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>44915</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45181</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45526</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45572</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45736</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45243</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44930</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45091</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45029</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45400</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45400</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45751</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45376</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45491</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45223</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45555</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45000</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45034</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44981</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45566</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>44958</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44958</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45210</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45371</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45322</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44806</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>45530</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45062</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44517</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45002</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>44964</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45111</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45275</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45020</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45538</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45544</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44579</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45107</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44987</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>45370</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45585</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45588</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45191</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45751</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45560</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45334</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45021</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>44806</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>45509</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45160</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45420</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45181</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45610</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44603</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45726</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45726</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45167</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45091</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45636</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45609</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45211</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45751</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45362</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45407</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45191</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45376</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>44616</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45250</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45400</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45300</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45167</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45180</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44797</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>44979</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45361</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45082</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45763</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>44698</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>45359</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45610</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45561</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45391</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45559</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>44953</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45432</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>44859</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45069</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45069</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44711</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44658</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44658</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44630</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>44711</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44706</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>44712</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44711</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44559</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44658</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44559</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44711</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44671</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45422</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45422</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44974</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44782</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>44967</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44967</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45002</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45369</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45008</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44993</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45422</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45015</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45422</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44980</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44990</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45427</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44997</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45422</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>45387</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44967</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45081</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44957</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45422</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45008</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44974</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45786</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45786</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45789</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45786</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45826</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45627</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45853</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45888</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45891</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45693</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45483</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>46081</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46083</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46099</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46100</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46119</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46206</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46289</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46289</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46294</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>46314</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46273</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SVENLJUNGA.xlsx
+++ b/Översikt SVENLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44579</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45734</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44800</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44711</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46296</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45726</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45345</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45173</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>46006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>46288</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44706</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44969</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44496</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44824</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44498</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44706</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44692</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44610</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44616</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44882</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>44792</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44789</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44797</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44796</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44530</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44883</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44515</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44638</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44706</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44658</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45054</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44859</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45180</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45785</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45888</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45884</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44658</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45734</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44988</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45898</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45898</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44564</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45211</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45363</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45904</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45099</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45411</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45911</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45316</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45274</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45911</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>46164</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>46163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45111</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>46163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>46168</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44964</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45726</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>46169</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>46169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45834</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45785</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45763</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45099</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45370</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>46175</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46175</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45266</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45938</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>46174</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>46175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>46174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44837</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44849</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44902</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44855</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45485</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44860</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45386</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45082</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45250</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45411</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45420</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44830</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44953</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45069</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45267</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45952</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45953</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45569</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45621</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45211</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45953</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45644</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45751</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45354</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45737</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45411</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45964</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45720</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45968</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45726</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45726</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45645</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45572</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45474</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44981</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46196</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44898</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45609</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45433</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44617</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46199</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46199</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44517</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45726</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45979</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45982</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>46205</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45114</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>44574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45000</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45609</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45489</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>44837</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>46209</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>46209</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45194</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45952</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45995</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>46001</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46002</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45705</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46002</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>46002</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46006</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45342</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46006</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46006</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46231</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45523</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45120</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45784</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46008</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>46009</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>46279</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45629</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45086</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45701</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45693</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45709</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45384</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45572</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45266</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45531</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45791</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>46282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>46286</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>46286</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45791</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45559</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45211</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45358</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>46289</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45810</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45810</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46293</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45814</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46294</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>46064</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46294</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>46286</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45726</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46072</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45820</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46066</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46066</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45824</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45824</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46066</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45825</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>46078</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>46079</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45737</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45736</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45726</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45726</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45737</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45726</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45827</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45737</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>46251</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45048</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>46085</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46085</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45832</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45832</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>46085</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46085</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45834</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45834</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46090</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46254</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>46092</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45840</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46183</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45485</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46297</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>46094</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>46199</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45785</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45846</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46301</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46301</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45485</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45485</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>46259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45854</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45615</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>46106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>46111</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44981</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44872</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45474</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45160</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45868</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45867</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45615</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>46120</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>46260</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45043</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45803</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46304</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46304</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45877</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>46306</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45734</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>44613</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>46259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44614</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45357</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45354</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>46092</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44964</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45518</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>46267</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>46267</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>46267</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46267</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45884</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45735</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45747</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45516</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>45972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45544</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45120</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45791</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45867</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>46269</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45432</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46253</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46274</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44950</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44942</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45775</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45194</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45747</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45790</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45789</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>46315</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45688</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45831</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>46315</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45797</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>46273</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45698</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>46253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>46274</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>46142</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46142</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45547</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45547</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45588</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46274</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46142</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45021</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46274</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46146</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45390</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46274</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45453</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46150</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>44987</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46149</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46149</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44754</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>46149</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>45737</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45559</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45251</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45988</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45738</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45069</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45098</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45629</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>44981</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45609</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45594</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44897</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45056</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44494</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45166</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>44970</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45565</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45630</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45000</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45645</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45149</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45736</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>44970</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>45120</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44804</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>44832</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44895</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45742</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45224</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45176</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45678</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45236</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45236</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45730</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>44937</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>44915</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45181</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45526</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45572</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45736</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45243</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44930</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45091</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45029</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45400</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45400</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45751</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45376</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45491</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45223</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45555</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45000</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45034</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44981</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45566</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>44958</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44958</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45210</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45371</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45322</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44806</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>45530</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45062</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44517</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45002</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>44964</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45111</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45275</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45020</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45538</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45544</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44579</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45107</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44987</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>45370</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45585</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45588</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45191</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45751</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45560</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45334</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45021</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>44806</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>45509</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45160</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45420</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45181</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45610</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44603</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45726</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45726</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45167</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45091</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45636</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45609</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45211</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45751</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45362</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45407</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45191</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45376</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>44616</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45250</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45400</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45300</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45167</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45180</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44797</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>44979</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45361</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45082</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45763</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>44698</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>45359</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45610</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45561</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45391</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45559</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>44953</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45432</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>44859</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45069</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45069</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44711</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44658</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44658</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44630</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>44711</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44706</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>44712</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44711</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44559</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44658</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44559</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44711</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44671</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45422</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45422</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44974</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44782</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>44967</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44967</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45002</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45369</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45008</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44993</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45422</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45015</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45422</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44980</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44990</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45427</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44997</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45422</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>45387</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44967</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45081</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44957</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45422</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45008</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44974</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45786</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45786</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45789</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45786</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45826</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45627</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45853</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45888</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45891</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45693</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45483</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>46081</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46081</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46083</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46083</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46099</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46100</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>46119</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46206</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46289</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46289</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46294</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>46314</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46273</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
